--- a/reports/seriemas_1/perfil_estatistico_anual.xlsx
+++ b/reports/seriemas_1/perfil_estatistico_anual.xlsx
@@ -16,21 +16,24 @@
     <sheet name="OMITIDOS" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="CONF_NAO_APLICAVEIS" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="PARAMETROS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="REN_FC_ANUAL" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="REN_FC_MENSAL" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="REN_CORTE_ANUAL" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="REN_CORTE_MENSAL" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="REN_CORTE_RAZAO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="REN_RECURSO_FAIXAS" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="CONF_G1_PARES" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="CONF_G1_MENSAL" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="CONF_G2_MENSAL" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CONF_G2_DIVERGENCIAS" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="CONF_G5_MENSAL" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="CAD_FICHA" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="CAD_AUDITORIA" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="DICIONARIOS" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="FONTES" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="PROG_RESUMO_MENSAL" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PROG_EVENTOS_DESVIO" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="REN_FC_ANUAL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="REN_FC_MENSAL" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="REN_CORTE_ANUAL" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="REN_CORTE_MENSAL" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="REN_CORTE_RAZAO" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="REN_RECURSO_FAIXAS" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="REN_DESVIOS_PROGRAMACAO" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="CONF_G1_PARES" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CONF_G1_MENSAL" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CONF_G2_MENSAL" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="CONF_G2_DIVERGENCIAS" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="CONF_G5_MENSAL" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="CAD_FICHA" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="CAD_AUDITORIA" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="DICIONARIOS" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="FONTES" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -498,46 +501,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fator de capacidade</t>
+          <t>Programação diária do ONS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fator de capacidade publicado pelo ONS de 16,7% de 22/08/2026 a 19/10/2026, no nível conjunto de usinas, em 1.416 horas.</t>
+          <t>Nas 1.296 horas com programação e geração verificada do conjunto Conj. Inocência 230 kV, geração verificada média de 69,6 MW e programada de 40,8 MW (desvio médio absoluto de 43,9 MW; correlação de 0,63); 4 horas com geração até 1 MW e programação acima de 5 MW.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energia cortada</t>
+          <t>Fator de capacidade</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Energia cortada por restrição de operação de 1.127 MWh nas 814 semi-horas com a marca de restrição (16,3% da energia estimada nas semi-horas com a marca); diferença bruta entre a estimada e a verificada de 2.428 MWh em todas as semi-horas. Sem a estimativa do ONS (estimada 0 com a usina gerando) em 500 semi-horas, 385 delas com a marca de restrição, em que o corte não pôde ser calculado.</t>
+          <t>Fator de capacidade publicado pelo ONS de 16,7% de 22/08/2026 a 19/10/2026, no nível conjunto de usinas, em 1.416 horas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recurso × geração</t>
+          <t>Energia cortada</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas (19,9%), fora das faixas.</t>
+          <t>Energia cortada por restrição de operação de 1.127 MWh nas 814 semi-horas com a marca de restrição (16,3% da energia estimada nas semi-horas com a marca); diferença bruta entre a estimada e a verificada de 2.428 MWh em todas as semi-horas. Sem a estimativa do ONS (estimada 0 com a usina gerando) em 500 semi-horas, 385 delas com a marca de restrição, em que o corte não pôde ser calculado.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Recurso × geração</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas (19,9%), fora das faixas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Qualidade dos dados</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Nenhuma hora sinalizada na base horária.</t>
         </is>
@@ -549,6 +564,219 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>horas_comuns</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>geracao_media_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>programada_media_mw</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>desvio_medio_mw</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>desvio_medio_absoluto_mw</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>horas_desvio_programacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" t="n">
+        <v>82.20726666666665</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>82.20726666666665</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82.20726666666665</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3" t="n">
+        <v>720</v>
+      </c>
+      <c r="C3" t="n">
+        <v>68.72983402777777</v>
+      </c>
+      <c r="D3" t="n">
+        <v>42.25694444444444</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.47288958333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39.47373263888889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4" t="n">
+        <v>456</v>
+      </c>
+      <c r="C4" t="n">
+        <v>67.65447807017544</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49.13925438596491</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.51522368421053</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40.81308114035087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fim</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>duracao_h</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>programacao_media_mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46295.25</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46295.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46304.66666666666</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46304.70833333334</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46308.70833333334</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46308.70833333334</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -651,7 +879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -801,7 +1029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -938,7 +1166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1217,7 +1445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1286,7 +1514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1521,7 +1749,259 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>din_instante</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>geracao_programada_mw</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>geracao_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desvio_mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46267.58333333334</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>391.3095</v>
+      </c>
+      <c r="D2" t="n">
+        <v>391.3095</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46267.625</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>388.6385</v>
+      </c>
+      <c r="D3" t="n">
+        <v>388.6385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46268.625</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>386.31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46267.33333333334</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>377.784</v>
+      </c>
+      <c r="D5" t="n">
+        <v>377.784</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46267.41666666666</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>376.3165</v>
+      </c>
+      <c r="D6" t="n">
+        <v>376.3165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46267.45833333334</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>374.988</v>
+      </c>
+      <c r="D7" t="n">
+        <v>374.988</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46262.58333333334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>364.955</v>
+      </c>
+      <c r="D8" t="n">
+        <v>364.955</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46261.45833333334</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>352.705</v>
+      </c>
+      <c r="D9" t="n">
+        <v>352.705</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46261.41666666666</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>350</v>
+      </c>
+      <c r="D10" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46262.625</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>350</v>
+      </c>
+      <c r="D11" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46263.375</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>348.073</v>
+      </c>
+      <c r="D12" t="n">
+        <v>348.073</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46263.41666666666</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>347.927</v>
+      </c>
+      <c r="D13" t="n">
+        <v>347.927</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46261.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>346.836</v>
+      </c>
+      <c r="D14" t="n">
+        <v>346.836</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46261.375</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>344.0525</v>
+      </c>
+      <c r="D15" t="n">
+        <v>344.0525</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46268.66666666666</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>338.408</v>
+      </c>
+      <c r="D16" t="n">
+        <v>338.408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1728,7 +2208,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lista</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ordem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>regra</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>secoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pontos de atenção</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Energia cortada por restrição de operação de 1.127 MWh, 16,3% da energia estimada nas semi-horas com a marca de restrição</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7. Energia cortada por restrição de operação (constrained-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A verificar em campo</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas da usina (19,9%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8. Recurso × geração</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2199,7 +2777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2349,7 +2927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3434,105 +4012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>lista</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ordem</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>regra</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>secoes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Pontos de atenção</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Energia cortada por restrição de operação de 1.127 MWh, 16,3% da energia estimada nas semi-horas com a marca de restrição</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7. Energia cortada por restrição de operação (constrained-off)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A verificar em campo</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas da usina (19,9%)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>8. Recurso × geração</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3682,7 +4162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3859,7 +4339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3964,7 +4444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4832,13 +5312,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5121,22 +5601,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REN_FC_ANUAL</t>
+          <t>PROG_RESUMO_MENSAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>geração</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5148,22 +5628,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REN_FC_MENSAL</t>
+          <t>PROG_EVENTOS_DESVIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>geração</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5175,22 +5655,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REN_CORTE_ANUAL</t>
+          <t>REN_FC_ANUAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>geração estimada e marca de restrição</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5202,22 +5682,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REN_CORTE_MENSAL</t>
+          <t>REN_FC_MENSAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>geração estimada e marca de restrição</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5229,17 +5709,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REN_CORTE_RAZAO</t>
+          <t>REN_CORTE_ANUAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5256,12 +5736,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REN_RECURSO_FAIXAS</t>
+          <t>REN_CORTE_MENSAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5271,7 +5751,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>vento ou irradiância</t>
+          <t>geração estimada e marca de restrição</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5283,12 +5763,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CONF_G1_PARES</t>
+          <t>REN_CORTE_RAZAO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5298,24 +5778,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>geração estimada e marca de restrição</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONF_G1_MENSAL</t>
+          <t>REN_RECURSO_FAIXAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5325,29 +5805,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vento ou irradiância</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONF_G2_MENSAL</t>
+          <t>REN_DESVIOS_PROGRAMACAO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5364,17 +5844,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONF_G2_DIVERGENCIAS</t>
+          <t>CONF_G1_PARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5391,17 +5871,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CONF_G5_MENSAL</t>
+          <t>CONF_G1_MENSAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5418,17 +5898,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAD_FICHA</t>
+          <t>CONF_G2_MENSAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW))</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5445,17 +5925,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CAD_AUDITORIA</t>
+          <t>CONF_G2_DIVERGENCIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5472,25 +5952,106 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>CONF_G5_MENSAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CAD_FICHA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CAD_AUDITORIA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>DICIONARIOS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>não</t>
         </is>
@@ -6314,7 +6875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6376,7 +6937,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Programação diária × geração verificada</t>
+          <t>Conferência da geração entre fontes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,31 +6947,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sem horas com a programação e a geração verificada no mesmo nível</t>
+          <t>seção ainda não gerada pelo pipeline; os resultados da G1, da G2 e da G5, quando aplicáveis, estão nas legendas de fonte das seções de eólica e solar e nas abas CONF_G1, CONF_G2 e CONF_G5 da planilha</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conferência da geração entre fontes</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>secao</t>
+          <t>regra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>seção ainda não gerada pelo pipeline; os resultados da G1, da G2 e da G5, quando aplicáveis, estão nas legendas de fonte das seções de eólica e solar e nas abas CONF_G1, CONF_G2 e CONF_G5 da planilha</t>
+          <t>sem o Fator de capacidade no nível da usina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6419,23 +6980,6 @@
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>sem o Fator de capacidade no nível da usina</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>regra</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>sem a Programação diária no nível da usina</t>
         </is>

--- a/reports/seriemas_1/perfil_estatistico_anual.xlsx
+++ b/reports/seriemas_1/perfil_estatistico_anual.xlsx
@@ -30,10 +30,13 @@
     <sheet name="CONF_G2_MENSAL" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="CONF_G2_DIVERGENCIAS" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="CONF_G5_MENSAL" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="CAD_FICHA" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="CAD_AUDITORIA" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="DICIONARIOS" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="FONTES" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="CONJ_TRECHOS" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="CONJ_COMPOSICAO" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="CONJ_MENSAL" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="CAD_FICHA" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="CAD_AUDITORIA" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="DICIONARIOS" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="FONTES" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -549,10 +552,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Composição do conjunto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>O conjunto Conj. Inocência 230 kV (CJU_MS4FINO) teve 1 composição no período: de 22/08/2026 a 19/10/2026, 8 usinas (UFV), geração média do conjunto de 66,7 MWmed. Os números são do conjunto, sem divisão entre as usinas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Qualidade dos dados</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Nenhuma hora sinalizada na base horária.</t>
         </is>
@@ -4168,6 +4183,557 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trecho</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fim</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>usinas</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tipos</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>horas_com_valor</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>energia_mwh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>geracao_media_mw</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>geracao_maxima_mw</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>potencia_somada_mw</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>usinas_sem_potencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46314.95833333334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="H2" t="n">
+        <v>94480.74549999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>66.72369032485875</v>
+      </c>
+      <c r="J2" t="n">
+        <v>393.3155</v>
+      </c>
+      <c r="K2" t="n">
+        <v>400</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trecho</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ceg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>usina</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>saida</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unidades</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>potencia_mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052257-0.01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Seriemas 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052258-9.01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Seriemas 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052259-7.01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seriemas 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052260-0.01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Seriemas 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052261-9.01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seriemas 5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052262-7.01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Seriemas 6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052263-5.01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Seriemas 7</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UFV.RS.MS.052264-3.01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Seriemas 8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UFV</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trecho</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>horas_com_valor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>geracao_media_mw</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>energia_mwh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>240</v>
+      </c>
+      <c r="D2" t="n">
+        <v>58.9367625</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14144.823</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>720</v>
+      </c>
+      <c r="D3" t="n">
+        <v>68.72983402777777</v>
+      </c>
+      <c r="E3" t="n">
+        <v>49485.4805</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>456</v>
+      </c>
+      <c r="D4" t="n">
+        <v>67.65447807017544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30850.442</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4339,7 +4905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4444,7 +5010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5306,756 +5872,6 @@
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>aba</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>conjuntos_origem</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>conferencias</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sem_outra_fonte</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>calculado_no_relatorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONSTATACOES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CONCLUSAO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BASE_ANUAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>geração</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BASE_MENSAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>geração</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BASE_HORA_DO_DIA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>geração</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TRECHOS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OMITIDOS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CONF_NAO_APLICAVEIS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PARAMETROS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PROG_RESUMO_MENSAL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>geração</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PROG_EVENTOS_DESVIO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>geração</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REN_FC_ANUAL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REN_FC_MENSAL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REN_CORTE_ANUAL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>geração estimada e marca de restrição</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REN_CORTE_MENSAL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>geração estimada e marca de restrição</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REN_CORTE_RAZAO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>geração estimada e marca de restrição</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REN_RECURSO_FAIXAS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>vento ou irradiância</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REN_DESVIOS_PROGRAMACAO</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CONF_G1_MENSAL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CONF_G2_MENSAL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CONF_G2_DIVERGENCIAS</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CONF_G5_MENSAL</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CAD_FICHA</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW))</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CAD_AUDITORIA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DICIONARIOS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6197,6 +6013,837 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>aba</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>conjuntos_origem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>conferencias</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sem_outra_fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>calculado_no_relatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CONSTATACOES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CONCLUSAO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BASE_ANUAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BASE_MENSAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BASE_HORA_DO_DIA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TRECHOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OMITIDOS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>parâmetros do projeto (origem na tabela de parâmetros)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONF_NAO_APLICAVEIS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>parâmetros do projeto (origem na tabela de parâmetros)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PARAMETROS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PROG_RESUMO_MENSAL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PROG_EVENTOS_DESVIO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REN_FC_ANUAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REN_FC_MENSAL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REN_CORTE_ANUAL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>geração estimada e marca de restrição</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REN_CORTE_MENSAL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>geração estimada e marca de restrição</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REN_CORTE_RAZAO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>geração estimada e marca de restrição</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REN_RECURSO_FAIXAS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>vento ou irradiância</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REN_DESVIOS_PROGRAMACAO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONF_G1_MENSAL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CONF_G2_MENSAL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONF_G2_DIVERGENCIAS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONF_G5_MENSAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONJ_TRECHOS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CONJ_COMPOSICAO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONJ_MENSAL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>geração</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CAD_FICHA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CAD_AUDITORIA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DICIONARIOS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6875,7 +7522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6920,7 +7567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Composição e geração do conjunto</t>
+          <t>Conferência da geração entre fontes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6930,31 +7577,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>seção ainda não gerada pelo pipeline; a composição por trecho está na Fonte e cobertura dos dados</t>
+          <t>seção ainda não gerada pelo pipeline; os resultados da G1, da G2 e da G5, quando aplicáveis, estão nas legendas de fonte das seções de eólica e solar e nas abas CONF_G1, CONF_G2 e CONF_G5 da planilha</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Conferência da geração entre fontes</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>secao</t>
+          <t>regra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>seção ainda não gerada pelo pipeline; os resultados da G1, da G2 e da G5, quando aplicáveis, estão nas legendas de fonte das seções de eólica e solar e nas abas CONF_G1, CONF_G2 e CONF_G5 da planilha</t>
+          <t>sem o Fator de capacidade no nível da usina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6963,23 +7610,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>sem o Fator de capacidade no nível da usina</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>regra</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>sem a Programação diária no nível da usina</t>
         </is>

--- a/reports/seriemas_1/perfil_estatistico_anual.xlsx
+++ b/reports/seriemas_1/perfil_estatistico_anual.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Série de referência: Restrição com detalhe (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), de 22/08/2026 00h a 19/10/2026 23h: 1.416 horas com registro de 1.416 no período (100,00%).</t>
+          <t>Série de referência: Restrição com detalhe (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), de 22/08/2026 00h a 27/10/2026 23h: 1.608 horas com registro de 1.608 no período (100,00%).</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No cadastro de modalidade das usinas do ONS (obtido em 21/10/2026), a usina consta como UFV SERIEMAS 1 (SAE), CEG UFV.RS.MS.052257-0.01, id ONS MSSRI1, modalidade TIPO II-C, centro de operação COSR-S, ponto de conexão SE Inocência 230 kV, potência autorizada de 2,5 MW, estado MS e situação na ANEEL "A". O cadastro tem 0 outras usinas com "Seriemas 1" no nome, excluídas pelo CEG. Divergências com os parâmetros do projeto: potência autorizada de 2,5 MW (projeto: 50 MW).</t>
+          <t>No cadastro de modalidade das usinas do ONS (obtido em 29/10/2026), a usina consta como UFV SERIEMAS 1 (SAE), CEG UFV.RS.MS.052257-0.01, id ONS MSSRI1, modalidade TIPO II-C, centro de operação COSR-S, ponto de conexão SE Inocência 230 kV, potência autorizada de 2,5 MW, estado MS e situação na ANEEL "A". O cadastro tem 0 outras usinas com "Seriemas 1" no nome, excluídas pelo CEG. Divergências com os parâmetros do projeto: potência autorizada de 2,5 MW (projeto: 50 MW).</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geração média de 8,6 MWmed nas 1.416 horas com valor (12.198 MWh); geração até 1 MW em 55,9% das horas.</t>
+          <t>Geração média de 8,7 MWmed nas 1.608 horas com valor (13.922 MWh); geração até 1 MW em 55,8% das horas.</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nas 1.296 horas com programação e geração verificada do conjunto Conj. Inocência 230 kV, geração verificada média de 69,6 MW e programada de 40,8 MW (desvio médio absoluto de 43,9 MW; correlação de 0,63); 4 horas com geração até 1 MW e programação acima de 5 MW.</t>
+          <t>Nas 1.488 horas com programação e geração verificada do conjunto Conj. Inocência 230 kV, geração verificada média de 70,6 MW e programada de 44,0 MW (desvio médio absoluto de 44,6 MW; correlação de 0,63); 16 horas com geração até 1 MW e programação acima de 5 MW.</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fator de capacidade publicado pelo ONS de 16,7% de 22/08/2026 a 19/10/2026, no nível conjunto de usinas, em 1.416 horas.</t>
+          <t>Fator de capacidade publicado pelo ONS de 17,0% de 22/08/2026 a 27/10/2026, no nível conjunto de usinas, em 1.608 horas.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Energia cortada por restrição de operação de 1.127 MWh nas 814 semi-horas com a marca de restrição (16,3% da energia estimada nas semi-horas com a marca); diferença bruta entre a estimada e a verificada de 2.428 MWh em todas as semi-horas. Sem a estimativa do ONS (estimada 0 com a usina gerando) em 500 semi-horas, 385 delas com a marca de restrição, em que o corte não pôde ser calculado.</t>
+          <t>Energia cortada por restrição de operação de 1.169 MWh nas 919 semi-horas com a marca de restrição (16,6% da energia estimada nas semi-horas com a marca); diferença bruta entre a estimada e a verificada de 2.534 MWh em todas as semi-horas. Sem a estimativa do ONS (estimada 0 com a usina gerando) em 833 semi-horas, 473 delas com a marca de restrição, em que o corte não pôde ser calculado.</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas (19,9%), fora das faixas.</t>
+          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 3.216 semi-horas (17,5%), fora das faixas.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>O conjunto Conj. Inocência 230 kV (CJU_MS4FINO) teve 1 composição no período: de 22/08/2026 a 19/10/2026, 8 usinas (UFV), geração média do conjunto de 66,7 MWmed. Os números são do conjunto, sem divisão entre as usinas.</t>
+          <t>O conjunto Conj. Inocência 230 kV (CJU_MS4FINO) teve 1 composição no período: de 22/08/2026 a 27/10/2026, 8 usinas (UFV), geração média do conjunto de 68,0 MWmed. Os números são do conjunto, sem divisão entre as usinas.</t>
         </is>
       </c>
     </row>
@@ -684,22 +684,22 @@
         <v>46296</v>
       </c>
       <c r="B4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="C4" t="n">
-        <v>67.65447807017544</v>
+        <v>70.57994290123457</v>
       </c>
       <c r="D4" t="n">
-        <v>49.13925438596491</v>
+        <v>54.16358024691358</v>
       </c>
       <c r="E4" t="n">
-        <v>18.51522368421053</v>
+        <v>16.41636265432099</v>
       </c>
       <c r="F4" t="n">
-        <v>40.81308114035087</v>
+        <v>43.37848919753086</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -784,6 +784,104 @@
       </c>
       <c r="D4" t="n">
         <v>67.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46310.66666666666</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46310.70833333334</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46311.58333333334</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46311.70833333334</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>108.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46314.75</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46314.75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46315.75</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46315.75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46316.75</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46316.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46318.66666666666</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46318.70833333334</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46320.70833333334</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46320.70833333334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46.5</v>
       </c>
     </row>
   </sheetData>
@@ -868,16 +966,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="D2" t="n">
-        <v>94480.917</v>
+        <v>109366.278</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>16.68095286016949</v>
+        <v>17.00346361940298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1021,16 +1119,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="D4" t="n">
-        <v>30850.484</v>
+        <v>45735.845</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>16.91364254385965</v>
+        <v>17.64500192901234</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1140,40 +1238,40 @@
         <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>2832</v>
+        <v>3216</v>
       </c>
       <c r="C2" t="n">
-        <v>814</v>
+        <v>919</v>
       </c>
       <c r="D2" t="n">
-        <v>407</v>
+        <v>459.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>500</v>
+        <v>833</v>
       </c>
       <c r="G2" t="n">
-        <v>385</v>
+        <v>473</v>
       </c>
       <c r="H2" t="n">
-        <v>7150.412499999999</v>
+        <v>7296.928</v>
       </c>
       <c r="I2" t="n">
-        <v>6899.427</v>
+        <v>7053.824000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>6899.427</v>
+        <v>7053.824000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1127.246</v>
+        <v>1169.1845</v>
       </c>
       <c r="L2" t="n">
-        <v>16.33825533627648</v>
+        <v>16.57518673559193</v>
       </c>
       <c r="M2" t="n">
-        <v>2428.0255</v>
+        <v>2534.051</v>
       </c>
     </row>
   </sheetData>
@@ -1407,40 +1505,40 @@
         <v>46296</v>
       </c>
       <c r="B4" t="n">
-        <v>912</v>
+        <v>1296</v>
       </c>
       <c r="C4" t="n">
-        <v>256</v>
+        <v>361</v>
       </c>
       <c r="D4" t="n">
-        <v>128</v>
+        <v>180.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="G4" t="n">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
-        <v>3192.221</v>
+        <v>3338.7365</v>
       </c>
       <c r="I4" t="n">
-        <v>3061.48</v>
+        <v>3215.877</v>
       </c>
       <c r="J4" t="n">
-        <v>3061.48</v>
+        <v>3215.877</v>
       </c>
       <c r="K4" t="n">
-        <v>597.866</v>
+        <v>639.8045000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>19.52865934123365</v>
+        <v>19.89517944871648</v>
       </c>
       <c r="M4" t="n">
-        <v>1217.759</v>
+        <v>1323.7845</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1449,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>597.866</v>
+        <v>639.8045</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1515,10 +1613,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>814</v>
+        <v>919</v>
       </c>
       <c r="D2" t="n">
-        <v>1127.246</v>
+        <v>1169.1845</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -1580,13 +1678,13 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1578</v>
+        <v>1801</v>
       </c>
       <c r="D2" t="n">
-        <v>4.318035487959442</v>
+        <v>3.898793448084398</v>
       </c>
       <c r="E2" t="n">
-        <v>4.534663994655978</v>
+        <v>3.632133611691023</v>
       </c>
     </row>
     <row r="3">
@@ -1597,13 +1695,13 @@
         <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D3" t="n">
-        <v>11.88016049382716</v>
+        <v>11.69059550561798</v>
       </c>
       <c r="E3" t="n">
-        <v>15.61914285714286</v>
+        <v>15.58647142857143</v>
       </c>
     </row>
     <row r="4">
@@ -1614,13 +1712,13 @@
         <v>300</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D4" t="n">
-        <v>13.56209803921569</v>
+        <v>13.13247540983606</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06903225806452</v>
+        <v>12.60960526315789</v>
       </c>
     </row>
     <row r="5">
@@ -1631,13 +1729,13 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>16.25148387096774</v>
+        <v>16.29208823529412</v>
       </c>
       <c r="E5" t="n">
-        <v>16.317625</v>
+        <v>15.34671111111111</v>
       </c>
     </row>
     <row r="6">
@@ -1648,13 +1746,13 @@
         <v>500</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>20.01785</v>
+        <v>19.52960975609756</v>
       </c>
       <c r="E6" t="n">
-        <v>19.48892307692308</v>
+        <v>19.89007407407408</v>
       </c>
     </row>
     <row r="7">
@@ -1665,13 +1763,13 @@
         <v>600</v>
       </c>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>14.98377358490566</v>
+        <v>16.41653731343283</v>
       </c>
       <c r="E7" t="n">
-        <v>11.87003448275862</v>
+        <v>11.49213513513513</v>
       </c>
     </row>
     <row r="8">
@@ -1682,13 +1780,13 @@
         <v>700</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>20.77925</v>
+        <v>22.06155555555555</v>
       </c>
       <c r="E8" t="n">
-        <v>14.73</v>
+        <v>14.53338888888889</v>
       </c>
     </row>
     <row r="9">
@@ -1699,13 +1797,13 @@
         <v>800</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>22.94856164383562</v>
+        <v>24.74956626506024</v>
       </c>
       <c r="E9" t="n">
-        <v>19.12153571428572</v>
+        <v>18.26028125</v>
       </c>
     </row>
     <row r="10">
@@ -1716,13 +1814,13 @@
         <v>900</v>
       </c>
       <c r="C10" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>23.290328</v>
+        <v>24.0941301369863</v>
       </c>
       <c r="E10" t="n">
-        <v>14.97514545454545</v>
+        <v>14.96882352941176</v>
       </c>
     </row>
     <row r="11">
@@ -1733,13 +1831,13 @@
         <v>1000</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>27.19704761904762</v>
+        <v>25.84393670886076</v>
       </c>
       <c r="E11" t="n">
-        <v>15.83057142857143</v>
+        <v>16.58084057971015</v>
       </c>
     </row>
     <row r="12">
@@ -1750,13 +1848,13 @@
         <v>1100</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>38.36608695652173</v>
+        <v>22.12602666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>9.603777777777777</v>
+        <v>19.11704</v>
       </c>
     </row>
   </sheetData>
@@ -1985,30 +2083,30 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46261.375</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>344.0525</v>
+        <v>383.0650000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>344.0525</v>
+        <v>346.0650000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46268.66666666666</v>
+        <v>46261.375</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>338.408</v>
+        <v>344.0525</v>
       </c>
       <c r="D16" t="n">
-        <v>338.408</v>
+        <v>344.0525</v>
       </c>
     </row>
   </sheetData>
@@ -2112,10 +2210,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="E2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2130,10 +2228,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>94480.74549999999</v>
+        <v>109366.1065</v>
       </c>
       <c r="K2" t="n">
-        <v>94480.917</v>
+        <v>109366.278</v>
       </c>
     </row>
     <row r="3">
@@ -2153,10 +2251,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="E3" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2171,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>94480.74549999999</v>
+        <v>109366.1065</v>
       </c>
       <c r="K3" t="n">
-        <v>94480.74549999999</v>
+        <v>109366.1065</v>
       </c>
     </row>
     <row r="4">
@@ -2194,10 +2292,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="E4" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2212,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>94480.917</v>
+        <v>109366.278</v>
       </c>
       <c r="K4" t="n">
-        <v>94480.74549999999</v>
+        <v>109366.1065</v>
       </c>
     </row>
   </sheetData>
@@ -2282,7 +2380,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Energia cortada por restrição de operação de 1.127 MWh, 16,3% da energia estimada nas semi-horas com a marca de restrição</t>
+          <t>Energia cortada por restrição de operação de 1.169 MWh, 16,6% da energia estimada nas semi-horas com a marca de restrição</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2307,7 +2405,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 2.832 semi-horas da usina (19,9%)</t>
+          <t>Medição de irradiância marcada como inválida pelo ONS em 564 das 3.216 semi-horas da usina (17,5%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2508,16 +2606,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="F4" t="n">
-        <v>30850.484</v>
+        <v>45735.845</v>
       </c>
       <c r="G4" t="n">
         <v>-0.04200000000128057</v>
       </c>
       <c r="H4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2637,16 +2735,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="F7" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2766,16 +2864,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30850.484</v>
+        <v>45735.845</v>
       </c>
       <c r="F10" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="G10" t="n">
         <v>0.04200000000128057</v>
       </c>
       <c r="H10" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2916,16 +3014,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="C4" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -4151,16 +4249,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22407.5</v>
+        <v>35098</v>
       </c>
       <c r="C4" t="n">
-        <v>22407.5</v>
+        <v>35098</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -4270,7 +4368,7 @@
         <v>46256</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46314.95833333334</v>
+        <v>46322.95833333334</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -4281,19 +4379,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="G2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="H2" t="n">
-        <v>94480.74549999999</v>
+        <v>109366.1065</v>
       </c>
       <c r="I2" t="n">
-        <v>66.72369032485875</v>
+        <v>68.01374782338308</v>
       </c>
       <c r="J2" t="n">
-        <v>393.3155</v>
+        <v>391.415</v>
       </c>
       <c r="K2" t="n">
         <v>400</v>
@@ -4714,13 +4812,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="D4" t="n">
-        <v>67.65447807017544</v>
+        <v>70.57994290123457</v>
       </c>
       <c r="E4" t="n">
-        <v>30850.442</v>
+        <v>45735.803</v>
       </c>
     </row>
   </sheetData>
@@ -4877,7 +4975,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:46:58</t>
+          <t>2026-10-29 14:16:36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4984,7 +5082,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6024</v>
+        <v>6048</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -5122,7 +5220,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:18</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5171,7 +5269,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:18</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5220,7 +5318,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:23</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5269,7 +5367,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:23</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5318,7 +5416,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:26</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5367,7 +5465,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:26</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5416,7 +5514,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:29</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5465,7 +5563,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:29</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5514,7 +5612,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:32</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5563,7 +5661,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:32</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5612,7 +5710,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:36</t>
+          <t>2026-10-29 14:58:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5661,7 +5759,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-21 13:18:36</t>
+          <t>2026-10-29 14:58:46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5710,7 +5808,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-21 13:10:59</t>
+          <t>2026-10-29 14:55:47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5759,7 +5857,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-21 13:10:59</t>
+          <t>2026-10-29 14:55:47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5808,7 +5906,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:03</t>
+          <t>2026-10-29 14:55:50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5857,7 +5955,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-21 13:11:03</t>
+          <t>2026-10-29 14:55:50</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5982,28 +6080,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="E2" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="F2" t="n">
-        <v>8.614753531073447</v>
+        <v>8.657860074626866</v>
       </c>
       <c r="G2" t="n">
-        <v>12198.491</v>
+        <v>13921.839</v>
       </c>
       <c r="H2" t="n">
-        <v>49.228</v>
+        <v>49.17</v>
       </c>
       <c r="I2" t="n">
-        <v>792</v>
+        <v>898</v>
       </c>
       <c r="J2" t="n">
-        <v>55.93220338983051</v>
+        <v>55.84577114427861</v>
       </c>
       <c r="K2" t="n">
-        <v>17.22950706214689</v>
+        <v>17.31572014925373</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -6064,12 +6162,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6091,12 +6189,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: divergências (potência autorizada de 2,5 MW (projeto: 50 MW)); geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma; programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6118,12 +6216,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6145,7 +6243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6172,7 +6270,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6199,7 +6297,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6280,7 +6378,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6307,12 +6405,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6334,12 +6432,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6361,12 +6459,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6388,12 +6486,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6415,12 +6513,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES; soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6442,12 +6540,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6469,12 +6567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6496,12 +6594,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6523,12 +6621,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6550,12 +6648,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6577,12 +6675,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.248 de 4.248 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
+          <t>geração conferida entre as fontes, duas a duas e no mesmo nível (G1): 4.824 de 4.824 horas coincidentes (100,0%) em 3 pares de fontes, detalhados na aba CONF_G1_PARES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6604,12 +6702,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6631,12 +6729,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6658,12 +6756,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.104 de 1.104 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado do Fator de capacidade (G5): 1.296 de 1.296 horas coincidentes (100,0%), 192 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6685,12 +6783,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6712,7 +6810,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6739,12 +6837,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG das usinas do conjunto CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.105 de 1.296 horas coincidentes (85,3%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
+          <t>soma das usinas do conjunto (Restrição com detalhe) conferida com a Geração por usina do conjunto (G2): 1.297 de 1.488 horas coincidentes (87,2%), 191 divergências, listadas na aba CONF_G2_DIVERGENCIAS; 120 horas sem todas as usinas, fora da soma</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6766,7 +6864,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6793,7 +6891,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026</t>
+          <t>Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6820,7 +6918,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 20/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 21/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 21/10/2026</t>
+          <t>Programação diária (conjunto de usinas, MS4FINO), obtido em 29/10/2026; Geração por usina (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Modalidade das usinas (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Capacidade de geração (CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Fator de capacidade (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026; Restrição com detalhe (constrained-off) (id ONS MSSRI1; CEG UFV.RS.MS.052257-0.01), obtido em 29/10/2026; Restrição com a razão (constrained-off) (conjunto de usinas, id ONS CJU_MS4FINO), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6947,16 +7045,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="D4" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="E4" t="n">
-        <v>8.791182017543859</v>
+        <v>8.845875000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>4008.779</v>
+        <v>5732.127</v>
       </c>
     </row>
   </sheetData>
@@ -7014,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -7030,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -7046,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -7062,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -7075,10 +7173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.001101694915254237</v>
+        <v>0.006044776119402986</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -7091,10 +7189,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2828813559322034</v>
+        <v>0.7957686567164178</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -7107,10 +7205,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.099076271186441</v>
+        <v>3.229888059701493</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -7123,10 +7221,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.462627118644066</v>
+        <v>10.10240298507463</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -7139,10 +7237,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.3074406779661</v>
+        <v>15.55507462686567</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
@@ -7155,10 +7253,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.94738983050847</v>
+        <v>17.27032835820896</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -7171,10 +7269,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.66925423728814</v>
+        <v>17.86547014925373</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -7187,10 +7285,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.03339830508475</v>
+        <v>19.43891791044776</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -7203,10 +7301,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.47172033898305</v>
+        <v>19.49598507462687</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -7219,10 +7317,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.59033898305085</v>
+        <v>22.80138059701493</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -7235,10 +7333,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.36253389830508</v>
+        <v>26.27715671641791</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -7251,10 +7349,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.1266779661017</v>
+        <v>26.76287313432836</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
@@ -7267,10 +7365,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.48024576271186</v>
+        <v>20.91967164179104</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
@@ -7283,10 +7381,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.753194915254237</v>
+        <v>7.092067164179104</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -7299,10 +7397,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1662033898305084</v>
+        <v>0.1756119402985075</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -7318,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -7334,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -7350,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
@@ -7366,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -7382,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -7476,7 +7574,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19 23:00:00</t>
+          <t>2026-10-27 23:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
